--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_114_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_114_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M2" t="n">
         <v>9</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M3" t="n">
         <v>9</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1531,7 +1531,7 @@
         <v>4</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
         <v>17</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
@@ -2119,10 +2119,10 @@
         <v>11</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2517,10 +2517,10 @@
         <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X23" t="n">
         <v>3</v>
@@ -2707,16 +2707,16 @@
         <v>26</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X24" t="n">
         <v>4</v>
@@ -2903,10 +2903,10 @@
         <v>23</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -3298,7 +3298,7 @@
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -3497,10 +3497,10 @@
         <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X28" t="n">
         <v>2</v>
@@ -3827,16 +3827,16 @@
         <v>136</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X30" t="n">
         <v>28</v>
@@ -4886,10 +4886,10 @@
         <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X38" t="n">
         <v>3</v>
@@ -5076,16 +5076,16 @@
         <v>13</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U39" t="n">
         <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X39" t="n">
         <v>9</v>
@@ -5468,7 +5468,7 @@
         <v>2</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
@@ -5664,10 +5664,10 @@
         <v>19</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -5863,7 +5863,7 @@
         <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -6059,7 +6059,7 @@
         <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -6454,10 +6454,10 @@
         <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X46" t="n">
         <v>3</v>
@@ -6784,16 +6784,16 @@
         <v>92</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="X48" t="n">
         <v>38</v>

--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_114_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_114_EL.xlsx
@@ -674,10 +674,10 @@
         <v>9</v>
       </c>
       <c r="N2" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="O2" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="P2" t="n">
         <v>8</v>
@@ -705,7 +705,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>90.32</t>
+          <t>84.21</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>9</v>
       </c>
       <c r="N3" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="O3" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="P3" t="n">
         <v>6</v>
@@ -864,7 +864,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>77.55</t>
+          <t>62.07</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1739,14 +1739,14 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA19" t="n">
@@ -1935,10 +1935,10 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
@@ -2523,10 +2523,10 @@
         <v>1</v>
       </c>
       <c r="X23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
@@ -2719,10 +2719,10 @@
         <v>1</v>
       </c>
       <c r="X24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
@@ -2915,14 +2915,14 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Y25" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="AA25" t="n">
@@ -3839,14 +3839,14 @@
         <v>4</v>
       </c>
       <c r="X30" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="Y30" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>90.3%</t>
+          <t>84.2%</t>
         </is>
       </c>
       <c r="AA30" t="n">
@@ -4892,14 +4892,14 @@
         <v>2</v>
       </c>
       <c r="X38" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA38" t="n">
@@ -5088,14 +5088,14 @@
         <v>2</v>
       </c>
       <c r="X39" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="Y39" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>81.8%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="AA39" t="n">
@@ -5480,14 +5480,14 @@
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA41" t="n">
@@ -5676,14 +5676,14 @@
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y42" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>87.5%</t>
         </is>
       </c>
       <c r="AA42" t="n">
@@ -5872,14 +5872,14 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA43" t="n">
@@ -6068,14 +6068,14 @@
         <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Y44" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="AA44" t="n">
@@ -6796,14 +6796,14 @@
         <v>5</v>
       </c>
       <c r="X48" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="Y48" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>62.1%</t>
         </is>
       </c>
       <c r="AA48" t="n">
